--- a/data/Nedel_ipc.xlsx
+++ b/data/Nedel_ipc.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="370">
   <si>
     <t>Содержание:</t>
   </si>
@@ -1209,6 +1209,9 @@
   <si>
     <t>на 27 июля</t>
   </si>
+  <si>
+    <t>на 3 августа</t>
+  </si>
 </sst>
 </file>
 
@@ -72625,7 +72628,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD120"/>
+  <dimension ref="A1:AE120"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="57.85546875" customWidth="1"/>
@@ -72640,16 +72643,16 @@
     <col min="15" max="16" width="18.140625" customWidth="1"/>
     <col min="17" max="21" width="17.5703125" customWidth="1"/>
     <col min="22" max="23" width="17.42578125" customWidth="1"/>
-    <col min="24" max="30" width="17" customWidth="1"/>
+    <col min="24" max="31" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>108</v>
       </c>
       <c r="B1" s="10"/>
     </row>
-    <row r="2" spans="1:30" ht="108.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" ht="108.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9"/>
       <c r="B2" s="33" t="s">
         <v>332</v>
@@ -72661,7 +72664,7 @@
       <c r="G2" s="33"/>
       <c r="H2" s="33"/>
     </row>
-    <row r="3" spans="1:30" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="34" t="s">
         <v>118</v>
       </c>
@@ -72672,7 +72675,7 @@
       <c r="G3" s="34"/>
       <c r="H3" s="34"/>
     </row>
-    <row r="4" spans="1:30" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>2</v>
       </c>
@@ -72763,8 +72766,11 @@
       <c r="AD4" s="12" t="s">
         <v>368</v>
       </c>
+      <c r="AE4" s="12" t="s">
+        <v>369</v>
+      </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>3</v>
       </c>
@@ -72855,8 +72861,11 @@
       <c r="AD5" s="31">
         <v>100.09</v>
       </c>
+      <c r="AE5" s="31">
+        <v>100.09</v>
+      </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>4</v>
       </c>
@@ -72947,8 +72956,11 @@
       <c r="AD6" s="31">
         <v>101.1</v>
       </c>
+      <c r="AE6" s="31">
+        <v>100.45</v>
+      </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>5</v>
       </c>
@@ -73039,8 +73051,11 @@
       <c r="AD7" s="31">
         <v>100.09</v>
       </c>
+      <c r="AE7" s="31">
+        <v>100.07</v>
+      </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>6</v>
       </c>
@@ -73131,8 +73146,11 @@
       <c r="AD8" s="31">
         <v>101.85</v>
       </c>
+      <c r="AE8" s="31">
+        <v>100.86</v>
+      </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>7</v>
       </c>
@@ -73223,8 +73241,11 @@
       <c r="AD9" s="31">
         <v>100.42</v>
       </c>
+      <c r="AE9" s="31">
+        <v>100.02</v>
+      </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>8</v>
       </c>
@@ -73315,8 +73336,11 @@
       <c r="AD10" s="31">
         <v>100.16</v>
       </c>
+      <c r="AE10" s="31">
+        <v>99.79</v>
+      </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>9</v>
       </c>
@@ -73407,8 +73431,11 @@
       <c r="AD11" s="31">
         <v>99.71</v>
       </c>
+      <c r="AE11" s="31">
+        <v>100.09</v>
+      </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>10</v>
       </c>
@@ -73499,8 +73526,11 @@
       <c r="AD12" s="31">
         <v>100.21</v>
       </c>
+      <c r="AE12" s="31">
+        <v>100.05</v>
+      </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>11</v>
       </c>
@@ -73591,8 +73621,11 @@
       <c r="AD13" s="31">
         <v>100.43</v>
       </c>
+      <c r="AE13" s="31">
+        <v>100.28</v>
+      </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>12</v>
       </c>
@@ -73683,8 +73716,11 @@
       <c r="AD14" s="31">
         <v>99.69</v>
       </c>
+      <c r="AE14" s="31">
+        <v>99.82</v>
+      </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>94</v>
       </c>
@@ -73775,8 +73811,11 @@
       <c r="AD15" s="31">
         <v>100.3</v>
       </c>
+      <c r="AE15" s="31">
+        <v>100.29</v>
+      </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>13</v>
       </c>
@@ -73867,8 +73906,11 @@
       <c r="AD16" s="31">
         <v>99.82</v>
       </c>
+      <c r="AE16" s="31">
+        <v>99.54</v>
+      </c>
     </row>
-    <row r="17" spans="1:30" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>14</v>
       </c>
@@ -73959,8 +74001,11 @@
       <c r="AD17" s="31">
         <v>99.94</v>
       </c>
+      <c r="AE17" s="31">
+        <v>99.93</v>
+      </c>
     </row>
-    <row r="18" spans="1:30" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>274</v>
       </c>
@@ -74051,8 +74096,11 @@
       <c r="AD18" s="31">
         <v>99.89</v>
       </c>
+      <c r="AE18" s="31">
+        <v>100.01</v>
+      </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>16</v>
       </c>
@@ -74143,8 +74191,11 @@
       <c r="AD19" s="31">
         <v>100.07</v>
       </c>
+      <c r="AE19" s="31">
+        <v>99.95</v>
+      </c>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>333</v>
       </c>
@@ -74235,8 +74286,11 @@
       <c r="AD20" s="31">
         <v>99.85</v>
       </c>
+      <c r="AE20" s="31">
+        <v>99.96</v>
+      </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>95</v>
       </c>
@@ -74327,8 +74381,11 @@
       <c r="AD21" s="31">
         <v>99.7</v>
       </c>
+      <c r="AE21" s="31">
+        <v>99.97</v>
+      </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>17</v>
       </c>
@@ -74419,8 +74476,11 @@
       <c r="AD22" s="31">
         <v>100.09</v>
       </c>
+      <c r="AE22" s="31">
+        <v>99.66</v>
+      </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>111</v>
       </c>
@@ -74511,8 +74571,11 @@
       <c r="AD23" s="31">
         <v>99.48</v>
       </c>
+      <c r="AE23" s="31">
+        <v>99.99</v>
+      </c>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>18</v>
       </c>
@@ -74603,8 +74666,11 @@
       <c r="AD24" s="31">
         <v>100.05</v>
       </c>
+      <c r="AE24" s="31">
+        <v>99.72</v>
+      </c>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>19</v>
       </c>
@@ -74695,8 +74761,11 @@
       <c r="AD25" s="31">
         <v>100.39</v>
       </c>
+      <c r="AE25" s="31">
+        <v>100.29</v>
+      </c>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
         <v>20</v>
       </c>
@@ -74787,8 +74856,11 @@
       <c r="AD26" s="31">
         <v>99.41</v>
       </c>
+      <c r="AE26" s="31">
+        <v>99.62</v>
+      </c>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
         <v>21</v>
       </c>
@@ -74879,8 +74951,11 @@
       <c r="AD27" s="31">
         <v>102</v>
       </c>
+      <c r="AE27" s="31">
+        <v>101.24</v>
+      </c>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
         <v>22</v>
       </c>
@@ -74971,8 +75046,11 @@
       <c r="AD28" s="31">
         <v>100.31</v>
       </c>
+      <c r="AE28" s="31">
+        <v>100.14</v>
+      </c>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
         <v>23</v>
       </c>
@@ -75063,8 +75141,11 @@
       <c r="AD29" s="31">
         <v>99.91</v>
       </c>
+      <c r="AE29" s="31">
+        <v>99.97</v>
+      </c>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
         <v>24</v>
       </c>
@@ -75155,8 +75236,11 @@
       <c r="AD30" s="31">
         <v>100.18</v>
       </c>
+      <c r="AE30" s="31">
+        <v>100.25</v>
+      </c>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
         <v>25</v>
       </c>
@@ -75247,8 +75331,11 @@
       <c r="AD31" s="31">
         <v>100.18</v>
       </c>
+      <c r="AE31" s="31">
+        <v>100.02</v>
+      </c>
     </row>
-    <row r="32" spans="1:30" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
         <v>26</v>
       </c>
@@ -75339,8 +75426,11 @@
       <c r="AD32" s="31">
         <v>100.37</v>
       </c>
+      <c r="AE32" s="31">
+        <v>100.17</v>
+      </c>
     </row>
-    <row r="33" spans="1:30" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
         <v>96</v>
       </c>
@@ -75431,8 +75521,11 @@
       <c r="AD33" s="31">
         <v>100.41</v>
       </c>
+      <c r="AE33" s="31">
+        <v>100.17</v>
+      </c>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
         <v>27</v>
       </c>
@@ -75523,8 +75616,11 @@
       <c r="AD34" s="31">
         <v>100.06</v>
       </c>
+      <c r="AE34" s="31">
+        <v>100.31</v>
+      </c>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
         <v>28</v>
       </c>
@@ -75615,8 +75711,11 @@
       <c r="AD35" s="31">
         <v>100.67</v>
       </c>
+      <c r="AE35" s="31">
+        <v>100.57</v>
+      </c>
     </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>29</v>
       </c>
@@ -75707,8 +75806,11 @@
       <c r="AD36" s="31">
         <v>101.21</v>
       </c>
+      <c r="AE36" s="31">
+        <v>101.37</v>
+      </c>
     </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
         <v>30</v>
       </c>
@@ -75799,8 +75901,11 @@
       <c r="AD37" s="31">
         <v>99.83</v>
       </c>
+      <c r="AE37" s="31">
+        <v>100.17</v>
+      </c>
     </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
         <v>31</v>
       </c>
@@ -75891,8 +75996,11 @@
       <c r="AD38" s="31">
         <v>100.18</v>
       </c>
+      <c r="AE38" s="31">
+        <v>100.01</v>
+      </c>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
         <v>32</v>
       </c>
@@ -75983,8 +76091,11 @@
       <c r="AD39" s="31">
         <v>98.04</v>
       </c>
+      <c r="AE39" s="31">
+        <v>97.48</v>
+      </c>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>33</v>
       </c>
@@ -76075,8 +76186,11 @@
       <c r="AD40" s="31">
         <v>97.74</v>
       </c>
+      <c r="AE40" s="31">
+        <v>96.68</v>
+      </c>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
         <v>34</v>
       </c>
@@ -76167,8 +76281,11 @@
       <c r="AD41" s="31">
         <v>98.94</v>
       </c>
+      <c r="AE41" s="31">
+        <v>99.01</v>
+      </c>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>97</v>
       </c>
@@ -76259,8 +76376,11 @@
       <c r="AD42" s="31">
         <v>99.04</v>
       </c>
+      <c r="AE42" s="31">
+        <v>98.61</v>
+      </c>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
         <v>35</v>
       </c>
@@ -76351,8 +76471,11 @@
       <c r="AD43" s="31">
         <v>99.44</v>
       </c>
+      <c r="AE43" s="31">
+        <v>97.74</v>
+      </c>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A44" s="13" t="s">
         <v>36</v>
       </c>
@@ -76443,8 +76566,11 @@
       <c r="AD44" s="31">
         <v>98.77</v>
       </c>
+      <c r="AE44" s="31">
+        <v>100.8</v>
+      </c>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
         <v>37</v>
       </c>
@@ -76535,8 +76661,11 @@
       <c r="AD45" s="31">
         <v>96.36</v>
       </c>
+      <c r="AE45" s="31">
+        <v>97.77</v>
+      </c>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
         <v>38</v>
       </c>
@@ -76627,8 +76756,11 @@
       <c r="AD46" s="31">
         <v>100.95</v>
       </c>
+      <c r="AE46" s="31">
+        <v>100.71</v>
+      </c>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A47" s="13" t="s">
         <v>98</v>
       </c>
@@ -76719,8 +76851,11 @@
       <c r="AD47" s="31">
         <v>100.77</v>
       </c>
+      <c r="AE47" s="31">
+        <v>100.7</v>
+      </c>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A48" s="13" t="s">
         <v>112</v>
       </c>
@@ -76811,8 +76946,11 @@
       <c r="AD48" s="31">
         <v>100.21</v>
       </c>
+      <c r="AE48" s="31">
+        <v>100.05</v>
+      </c>
     </row>
-    <row r="49" spans="1:30" ht="30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
         <v>39</v>
       </c>
@@ -76903,8 +77041,11 @@
       <c r="AD49" s="31">
         <v>100.14</v>
       </c>
+      <c r="AE49" s="31">
+        <v>100.08</v>
+      </c>
     </row>
-    <row r="50" spans="1:30" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
         <v>40</v>
       </c>
@@ -76995,8 +77136,11 @@
       <c r="AD50" s="31">
         <v>100.05</v>
       </c>
+      <c r="AE50" s="31">
+        <v>100.29</v>
+      </c>
     </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
         <v>41</v>
       </c>
@@ -77087,8 +77231,11 @@
       <c r="AD51" s="31">
         <v>100.92</v>
       </c>
+      <c r="AE51" s="31">
+        <v>100.62</v>
+      </c>
     </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
         <v>42</v>
       </c>
@@ -77179,8 +77326,11 @@
       <c r="AD52" s="31">
         <v>100.28</v>
       </c>
+      <c r="AE52" s="31">
+        <v>100.89</v>
+      </c>
     </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
         <v>43</v>
       </c>
@@ -77271,8 +77421,11 @@
       <c r="AD53" s="31">
         <v>99.87</v>
       </c>
+      <c r="AE53" s="31">
+        <v>100.48</v>
+      </c>
     </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
         <v>44</v>
       </c>
@@ -77363,8 +77516,11 @@
       <c r="AD54" s="31">
         <v>100.37</v>
       </c>
+      <c r="AE54" s="31">
+        <v>100.25</v>
+      </c>
     </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
         <v>45</v>
       </c>
@@ -77455,8 +77611,11 @@
       <c r="AD55" s="31">
         <v>100.07</v>
       </c>
+      <c r="AE55" s="31">
+        <v>100.35</v>
+      </c>
     </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A56" s="13" t="s">
         <v>46</v>
       </c>
@@ -77547,8 +77706,11 @@
       <c r="AD56" s="31">
         <v>99.95</v>
       </c>
+      <c r="AE56" s="31">
+        <v>100.8</v>
+      </c>
     </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
         <v>99</v>
       </c>
@@ -77639,8 +77801,11 @@
       <c r="AD57" s="31">
         <v>99.9</v>
       </c>
+      <c r="AE57" s="31">
+        <v>99.93</v>
+      </c>
     </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
         <v>100</v>
       </c>
@@ -77731,8 +77896,11 @@
       <c r="AD58" s="31">
         <v>99.75</v>
       </c>
+      <c r="AE58" s="31">
+        <v>100.01</v>
+      </c>
     </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
         <v>47</v>
       </c>
@@ -77823,8 +77991,11 @@
       <c r="AD59" s="31">
         <v>100.06</v>
       </c>
+      <c r="AE59" s="31">
+        <v>100.08</v>
+      </c>
     </row>
-    <row r="60" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A60" s="13" t="s">
         <v>48</v>
       </c>
@@ -77915,8 +78086,11 @@
       <c r="AD60" s="31">
         <v>100.2</v>
       </c>
+      <c r="AE60" s="31">
+        <v>100.18</v>
+      </c>
     </row>
-    <row r="61" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A61" s="13" t="s">
         <v>49</v>
       </c>
@@ -78007,8 +78181,11 @@
       <c r="AD61" s="31">
         <v>99.88</v>
       </c>
+      <c r="AE61" s="31">
+        <v>100.25</v>
+      </c>
     </row>
-    <row r="62" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
         <v>50</v>
       </c>
@@ -78099,8 +78276,11 @@
       <c r="AD62" s="31">
         <v>99.67</v>
       </c>
+      <c r="AE62" s="31">
+        <v>100.53</v>
+      </c>
     </row>
-    <row r="63" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A63" s="13" t="s">
         <v>51</v>
       </c>
@@ -78191,8 +78371,11 @@
       <c r="AD63" s="31">
         <v>99.86</v>
       </c>
+      <c r="AE63" s="31">
+        <v>99.8</v>
+      </c>
     </row>
-    <row r="64" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A64" s="13" t="s">
         <v>52</v>
       </c>
@@ -78283,8 +78466,11 @@
       <c r="AD64" s="31">
         <v>100.29</v>
       </c>
+      <c r="AE64" s="31">
+        <v>100.06</v>
+      </c>
     </row>
-    <row r="65" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A65" s="13" t="s">
         <v>101</v>
       </c>
@@ -78375,8 +78561,11 @@
       <c r="AD65" s="31">
         <v>100.27</v>
       </c>
+      <c r="AE65" s="31">
+        <v>100.09</v>
+      </c>
     </row>
-    <row r="66" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A66" s="13" t="s">
         <v>53</v>
       </c>
@@ -78467,8 +78656,11 @@
       <c r="AD66" s="31">
         <v>100.86</v>
       </c>
+      <c r="AE66" s="31">
+        <v>99.77</v>
+      </c>
     </row>
-    <row r="67" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A67" s="13" t="s">
         <v>54</v>
       </c>
@@ -78559,8 +78751,11 @@
       <c r="AD67" s="31">
         <v>100.57</v>
       </c>
+      <c r="AE67" s="31">
+        <v>100.09</v>
+      </c>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A68" s="13" t="s">
         <v>55</v>
       </c>
@@ -78651,8 +78846,11 @@
       <c r="AD68" s="31">
         <v>100.52</v>
       </c>
+      <c r="AE68" s="31">
+        <v>100.01</v>
+      </c>
     </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A69" s="13" t="s">
         <v>102</v>
       </c>
@@ -78743,8 +78941,11 @@
       <c r="AD69" s="31">
         <v>99.96</v>
       </c>
+      <c r="AE69" s="31">
+        <v>100.15</v>
+      </c>
     </row>
-    <row r="70" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A70" s="13" t="s">
         <v>56</v>
       </c>
@@ -78835,8 +79036,11 @@
       <c r="AD70" s="31">
         <v>99.91</v>
       </c>
+      <c r="AE70" s="31">
+        <v>99.78</v>
+      </c>
     </row>
-    <row r="71" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A71" s="13" t="s">
         <v>103</v>
       </c>
@@ -78927,8 +79131,11 @@
       <c r="AD71" s="31">
         <v>100.15</v>
       </c>
+      <c r="AE71" s="31">
+        <v>100.27</v>
+      </c>
     </row>
-    <row r="72" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A72" s="13" t="s">
         <v>57</v>
       </c>
@@ -79019,8 +79226,11 @@
       <c r="AD72" s="31">
         <v>100.22</v>
       </c>
+      <c r="AE72" s="31">
+        <v>100.62</v>
+      </c>
     </row>
-    <row r="73" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="13" t="s">
         <v>58</v>
       </c>
@@ -79111,8 +79321,11 @@
       <c r="AD73" s="31">
         <v>99.99</v>
       </c>
+      <c r="AE73" s="31">
+        <v>100.13</v>
+      </c>
     </row>
-    <row r="74" spans="1:30" ht="30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="13" t="s">
         <v>59</v>
       </c>
@@ -79203,8 +79416,11 @@
       <c r="AD74" s="31">
         <v>100.19</v>
       </c>
+      <c r="AE74" s="31">
+        <v>100.2</v>
+      </c>
     </row>
-    <row r="75" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A75" s="13" t="s">
         <v>60</v>
       </c>
@@ -79295,8 +79511,11 @@
       <c r="AD75" s="31">
         <v>100</v>
       </c>
+      <c r="AE75" s="31">
+        <v>100</v>
+      </c>
     </row>
-    <row r="76" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A76" s="13" t="s">
         <v>61</v>
       </c>
@@ -79387,8 +79606,11 @@
       <c r="AD76" s="31">
         <v>100</v>
       </c>
+      <c r="AE76" s="31">
+        <v>100.06</v>
+      </c>
     </row>
-    <row r="77" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A77" s="13" t="s">
         <v>62</v>
       </c>
@@ -79479,8 +79701,11 @@
       <c r="AD77" s="31">
         <v>99.94</v>
       </c>
+      <c r="AE77" s="31">
+        <v>98.43</v>
+      </c>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A78" s="13" t="s">
         <v>63</v>
       </c>
@@ -79571,8 +79796,11 @@
       <c r="AD78" s="31">
         <v>100.56</v>
       </c>
+      <c r="AE78" s="31">
+        <v>98.91</v>
+      </c>
     </row>
-    <row r="79" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A79" s="13" t="s">
         <v>64</v>
       </c>
@@ -79663,8 +79891,11 @@
       <c r="AD79" s="31">
         <v>100.42</v>
       </c>
+      <c r="AE79" s="31">
+        <v>98.89</v>
+      </c>
     </row>
-    <row r="80" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A80" s="13" t="s">
         <v>65</v>
       </c>
@@ -79755,8 +79986,11 @@
       <c r="AD80" s="31">
         <v>100.67</v>
       </c>
+      <c r="AE80" s="31">
+        <v>98.87</v>
+      </c>
     </row>
-    <row r="81" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
         <v>66</v>
       </c>
@@ -79847,8 +80081,11 @@
       <c r="AD81" s="31">
         <v>100.58</v>
       </c>
+      <c r="AE81" s="31">
+        <v>100.48</v>
+      </c>
     </row>
-    <row r="82" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A82" s="13" t="s">
         <v>334</v>
       </c>
@@ -79939,8 +80176,11 @@
       <c r="AD82" s="31">
         <v>99.92</v>
       </c>
+      <c r="AE82" s="31">
+        <v>99.87</v>
+      </c>
     </row>
-    <row r="83" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A83" s="13" t="s">
         <v>276</v>
       </c>
@@ -80031,8 +80271,11 @@
       <c r="AD83" s="31">
         <v>99.84</v>
       </c>
+      <c r="AE83" s="31">
+        <v>99.28</v>
+      </c>
     </row>
-    <row r="84" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A84" s="13" t="s">
         <v>277</v>
       </c>
@@ -80123,8 +80366,11 @@
       <c r="AD84" s="31">
         <v>100.08</v>
       </c>
+      <c r="AE84" s="31">
+        <v>99.71</v>
+      </c>
     </row>
-    <row r="85" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A85" s="13" t="s">
         <v>70</v>
       </c>
@@ -80215,8 +80461,11 @@
       <c r="AD85" s="31">
         <v>100.11</v>
       </c>
+      <c r="AE85" s="31">
+        <v>99.89</v>
+      </c>
     </row>
-    <row r="86" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A86" s="13" t="s">
         <v>71</v>
       </c>
@@ -80307,8 +80556,11 @@
       <c r="AD86" s="31">
         <v>100.17</v>
       </c>
+      <c r="AE86" s="31">
+        <v>99.6</v>
+      </c>
     </row>
-    <row r="87" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A87" s="13" t="s">
         <v>335</v>
       </c>
@@ -80399,8 +80651,11 @@
       <c r="AD87" s="31">
         <v>100.25</v>
       </c>
+      <c r="AE87" s="31">
+        <v>99.85</v>
+      </c>
     </row>
-    <row r="88" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A88" s="13" t="s">
         <v>280</v>
       </c>
@@ -80491,8 +80746,11 @@
       <c r="AD88" s="31">
         <v>100.41</v>
       </c>
+      <c r="AE88" s="31">
+        <v>100.04</v>
+      </c>
     </row>
-    <row r="89" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A89" s="13" t="s">
         <v>279</v>
       </c>
@@ -80583,8 +80841,11 @@
       <c r="AD89" s="31">
         <v>100.43</v>
       </c>
+      <c r="AE89" s="31">
+        <v>100.06</v>
+      </c>
     </row>
-    <row r="90" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A90" s="13" t="s">
         <v>113</v>
       </c>
@@ -80675,8 +80936,11 @@
       <c r="AD90" s="31">
         <v>99.88</v>
       </c>
+      <c r="AE90" s="31">
+        <v>99.72</v>
+      </c>
     </row>
-    <row r="91" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="13" t="s">
         <v>336</v>
       </c>
@@ -80767,8 +81031,11 @@
       <c r="AD91" s="31">
         <v>99.81</v>
       </c>
+      <c r="AE91" s="31">
+        <v>99.84</v>
+      </c>
     </row>
-    <row r="92" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A92" s="13" t="s">
         <v>74</v>
       </c>
@@ -80859,8 +81126,11 @@
       <c r="AD92" s="31">
         <v>100.09</v>
       </c>
+      <c r="AE92" s="31">
+        <v>100.47</v>
+      </c>
     </row>
-    <row r="93" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A93" s="13" t="s">
         <v>115</v>
       </c>
@@ -80951,8 +81221,11 @@
       <c r="AD93" s="31">
         <v>100.03</v>
       </c>
+      <c r="AE93" s="31">
+        <v>100.05</v>
+      </c>
     </row>
-    <row r="94" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A94" s="13" t="s">
         <v>116</v>
       </c>
@@ -81043,8 +81316,11 @@
       <c r="AD94" s="31">
         <v>100.25</v>
       </c>
+      <c r="AE94" s="31">
+        <v>100.05</v>
+      </c>
     </row>
-    <row r="95" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A95" s="13" t="s">
         <v>117</v>
       </c>
@@ -81135,8 +81411,11 @@
       <c r="AD95" s="31">
         <v>100.31</v>
       </c>
+      <c r="AE95" s="31">
+        <v>100.09</v>
+      </c>
     </row>
-    <row r="96" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A96" s="13" t="s">
         <v>75</v>
       </c>
@@ -81227,8 +81506,11 @@
       <c r="AD96" s="31">
         <v>100.06</v>
       </c>
+      <c r="AE96" s="31">
+        <v>100.11</v>
+      </c>
     </row>
-    <row r="97" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A97" s="13" t="s">
         <v>76</v>
       </c>
@@ -81319,8 +81601,11 @@
       <c r="AD97" s="31">
         <v>100</v>
       </c>
+      <c r="AE97" s="31">
+        <v>100</v>
+      </c>
     </row>
-    <row r="98" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A98" s="13" t="s">
         <v>77</v>
       </c>
@@ -81411,8 +81696,11 @@
       <c r="AD98" s="31">
         <v>100</v>
       </c>
+      <c r="AE98" s="31">
+        <v>100</v>
+      </c>
     </row>
-    <row r="99" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A99" s="13" t="s">
         <v>78</v>
       </c>
@@ -81503,8 +81791,11 @@
       <c r="AD99" s="31">
         <v>100</v>
       </c>
+      <c r="AE99" s="31">
+        <v>100</v>
+      </c>
     </row>
-    <row r="100" spans="1:30" ht="30" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
         <v>79</v>
       </c>
@@ -81595,8 +81886,11 @@
       <c r="AD100" s="31">
         <v>100.14</v>
       </c>
+      <c r="AE100" s="31">
+        <v>100.59</v>
+      </c>
     </row>
-    <row r="101" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A101" s="13" t="s">
         <v>86</v>
       </c>
@@ -81687,8 +81981,11 @@
       <c r="AD101" s="31">
         <v>100</v>
       </c>
+      <c r="AE101" s="31">
+        <v>100</v>
+      </c>
     </row>
-    <row r="102" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A102" s="13" t="s">
         <v>87</v>
       </c>
@@ -81779,8 +82076,11 @@
       <c r="AD102" s="31">
         <v>100</v>
       </c>
+      <c r="AE102" s="31">
+        <v>99.99</v>
+      </c>
     </row>
-    <row r="103" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A103" s="13" t="s">
         <v>88</v>
       </c>
@@ -81871,8 +82171,11 @@
       <c r="AD103" s="31">
         <v>100</v>
       </c>
+      <c r="AE103" s="31">
+        <v>100</v>
+      </c>
     </row>
-    <row r="104" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A104" s="13" t="s">
         <v>85</v>
       </c>
@@ -81963,8 +82266,11 @@
       <c r="AD104" s="31">
         <v>100</v>
       </c>
+      <c r="AE104" s="31">
+        <v>100</v>
+      </c>
     </row>
-    <row r="105" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A105" s="13" t="s">
         <v>90</v>
       </c>
@@ -82055,8 +82361,11 @@
       <c r="AD105" s="31">
         <v>100</v>
       </c>
+      <c r="AE105" s="31">
+        <v>100</v>
+      </c>
     </row>
-    <row r="106" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A106" s="13" t="s">
         <v>80</v>
       </c>
@@ -82147,8 +82456,11 @@
       <c r="AD106" s="31">
         <v>99.35</v>
       </c>
+      <c r="AE106" s="31">
+        <v>99.84</v>
+      </c>
     </row>
-    <row r="107" spans="1:30" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:31" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="13" t="s">
         <v>81</v>
       </c>
@@ -82239,8 +82551,11 @@
       <c r="AD107" s="31">
         <v>99.81</v>
       </c>
+      <c r="AE107" s="31">
+        <v>99.3</v>
+      </c>
     </row>
-    <row r="108" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A108" s="13" t="s">
         <v>82</v>
       </c>
@@ -82331,8 +82646,11 @@
       <c r="AD108" s="31">
         <v>99.62</v>
       </c>
+      <c r="AE108" s="31">
+        <v>99.07</v>
+      </c>
     </row>
-    <row r="109" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A109" s="13" t="s">
         <v>83</v>
       </c>
@@ -82423,8 +82741,11 @@
       <c r="AD109" s="31">
         <v>99.69</v>
       </c>
+      <c r="AE109" s="31">
+        <v>98.91</v>
+      </c>
     </row>
-    <row r="110" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A110" s="13" t="s">
         <v>84</v>
       </c>
@@ -82515,8 +82836,11 @@
       <c r="AD110" s="31">
         <v>100.09</v>
       </c>
+      <c r="AE110" s="31">
+        <v>99.5</v>
+      </c>
     </row>
-    <row r="111" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A111" s="13" t="s">
         <v>337</v>
       </c>
@@ -82607,8 +82931,11 @@
       <c r="AD111" s="31" t="s">
         <v>173</v>
       </c>
+      <c r="AE111" s="31" t="s">
+        <v>173</v>
+      </c>
     </row>
-    <row r="112" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A112" s="13" t="s">
         <v>352</v>
       </c>
@@ -82699,8 +83026,11 @@
       <c r="AD112" s="31">
         <v>92.04</v>
       </c>
+      <c r="AE112" s="31">
+        <v>100.36</v>
+      </c>
     </row>
-    <row r="113" spans="1:30" ht="30" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A113" s="13" t="s">
         <v>338</v>
       </c>
@@ -82791,8 +83121,11 @@
       <c r="AD113" s="31">
         <v>91.5</v>
       </c>
+      <c r="AE113" s="31">
+        <v>101.95</v>
+      </c>
     </row>
-    <row r="114" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A114" s="13" t="s">
         <v>91</v>
       </c>
@@ -82883,8 +83216,11 @@
       <c r="AD114" s="31">
         <v>99.55</v>
       </c>
+      <c r="AE114" s="31">
+        <v>98.61</v>
+      </c>
     </row>
-    <row r="115" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A115" s="13" t="s">
         <v>92</v>
       </c>
@@ -82975,8 +83311,11 @@
       <c r="AD115" s="31">
         <v>99.34</v>
       </c>
+      <c r="AE115" s="31">
+        <v>97.88</v>
+      </c>
     </row>
-    <row r="116" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A116" s="13" t="s">
         <v>282</v>
       </c>
@@ -83067,8 +83406,11 @@
       <c r="AD116" s="31">
         <v>100.25</v>
       </c>
+      <c r="AE116" s="31">
+        <v>100.09</v>
+      </c>
     </row>
-    <row r="117" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A117" s="29"/>
       <c r="B117" s="30"/>
       <c r="C117" s="30"/>
@@ -83083,7 +83425,7 @@
       <c r="L117" s="30"/>
       <c r="M117" s="30"/>
     </row>
-    <row r="118" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A118" s="20" t="s">
         <v>351</v>
       </c>
@@ -83097,12 +83439,12 @@
       <c r="I118" s="30"/>
       <c r="J118" s="30"/>
     </row>
-    <row r="119" spans="1:30" ht="39" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:31" ht="39" x14ac:dyDescent="0.25">
       <c r="A119" s="20" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="120" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A120" s="18" t="s">
         <v>233</v>
       </c>
